--- a/textbook_examples/mod01_sum_practice.xlsx
+++ b/textbook_examples/mod01_sum_practice.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="SUM example" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,41 +29,35 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FF4A7C59"/>
+      <color rgb="004A7C59"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF5C6B62"/>
+      <color rgb="005C6B62"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF24302A"/>
+      <color rgb="0024302A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <family val="2"/>
-      <color rgb="FF2F5D46"/>
+      <color rgb="002F5D46"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FF24302A"/>
+      <color rgb="0024302A"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -75,12 +70,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A7C59"/>
+        <fgColor rgb="004A7C59"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6EFD9"/>
+        <fgColor rgb="00F6EFD9"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,9 +91,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -118,14 +116,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -488,211 +484,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="12" min="1" max="1"/>
-    <col width="12" customWidth="1" style="12" min="2" max="2"/>
-    <col width="14" customWidth="1" style="12" min="3" max="3"/>
-    <col width="12" customWidth="1" style="12" min="4" max="4"/>
-    <col width="46" customWidth="1" style="12" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="12">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Ranges and the SUM function</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1" s="12">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Five fields of wheat.  Column B is the size of each field in acres and column C is its yield in bushels per acre.  Multiplying the two gives the bushels each field produced (column D).  To add those up we hand SUM a range — D5:D9 — rather than writing D5+D6+D7+D8+D9.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="12"/>
-    <row r="4" ht="18" customHeight="1" s="12">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Acres</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Yield (bu/ac)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Bushels</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" s="12">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="E4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>52.4</v>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="12">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>South</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>48.9</v>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1" s="12">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Creek</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>61.2</v>
       </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" s="12">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>310</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>55.7</v>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" s="12">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Rented</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>175</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>44.3</v>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="12">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="12"/>
-    <row r="12" ht="18" customHeight="1" s="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="8" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Mean acres per field, and mean bushels per field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>How many cells hold a NUMBER — blanks and text are skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Other ways to give SUM a range</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" s="12">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>One column</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>The five acre figures, B5 down to B9.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" s="12">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>One row</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Straight across row 5 — acres, yield and bushels. Rarely what you want.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" s="12">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Two ranges at once</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Separate ranges with a comma.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" s="12">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>A range plus a number</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Adds 40 acres of summerfallow that is not in the table.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" s="12"/>
+    <row r="19" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
